--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:48:21+00:00</t>
+    <t>2026-09-18T09:32:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:32:10+00:00</t>
+    <t>2026-09-18T11:05:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:59+00:00</t>
+    <t>2026-09-18T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:46:38+00:00</t>
+    <t>2026-09-18T12:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T12:07:35+00:00</t>
+    <t>2026-09-18T14:18:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T14:18:31+00:00</t>
+    <t>2026-09-18T14:33:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T14:33:14+00:00</t>
+    <t>2026-09-18T14:51:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T14:51:59+00:00</t>
+    <t>2026-09-21T07:38:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T07:38:15+00:00</t>
+    <t>2026-09-21T08:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T08:17:15+00:00</t>
+    <t>2026-09-21T08:39:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T08:39:37+00:00</t>
+    <t>2026-09-21T08:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T08:50:02+00:00</t>
+    <t>2026-09-21T09:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.6.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T09:00:44+00:00</t>
+    <t>2026-09-21T09:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T09:40:01+00:00</t>
+    <t>2026-09-21T12:03:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-21T12:03:18+00:00</t>
+    <t>2026-09-23T11:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-SYSTIntentionVS.xlsx
+++ b/ValueSet-SYSTIntentionVS.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.3</t>
+    <t>0.6.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:26:04+00:00</t>
+    <t>2026-10-22T11:42:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
